--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:12:31+00:00</t>
+    <t>2026-03-18T14:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:24:59+00:00</t>
+    <t>2026-03-31T06:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T06:24:20+00:00</t>
+    <t>2026-04-09T04:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T04:48:36+00:00</t>
+    <t>2026-04-15T07:47:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:47:05+00:00</t>
+    <t>2026-04-15T19:05:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}o-pat-req-1:The identifier element must contain the identifier for the Onconova logical pseudoidentifier slice. {identifier.where(type.coding.code = 'ACSN' and system = 'Onconova').exists()}o-pat-req-2:The identifier element must contain the identifier for the clinical center's patient identifier slice. {identifier.where(type.coding.code = 'MR').exists(system.exists() and value.exists())}o-pat-req-3:The gender element is required and must be provided {gender.exists()}o-pat-req-4:The birthDate element is required and must be provided {birthDate.exists() and birthDate.hasValue()}o-pat-req-5:The vital status extension is required and must be provided. {deceased.extension('http://hl7.org/fhir/StructureDefinition/onconova-ext-cancer-patient-vital-status').valueCodeableConcept.exists()}o-pat-req-6:If the patient is deceased, the date of death and cause of death must be provided. {deceasedDateTime.extension('http://hl7.org/fhir/StructureDefinition/onconova-ext-cancer-patient-vital-status').valueCodeableConcept.coding.code = '419099009' implies (deceasedDateTime.hasValue() and deceasedDateTime.extension('http://hl7.org/fhir/StructureDefinition/onconova-ext-cancer-patient-cause-of-death').valueCodeableConcept.exists())}o-pat-req-7:If the patient vital status is unknown, the end of records must be provided. {deceasedDateTime.extension('http://hl7.org/fhir/StructureDefinition/onconova-ext-cancer-patient-vital-status').valueCodeableConcept.coding.code = '261665006' implies extension('http://hl7.org/fhir/StructureDefinition/onconova-ext-cancer-patient-end-of-records').valueDate.hasValue()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}o-pat-req-1:The identifier element must contain the identifier for the Onconova logical pseudoidentifier slice. {identifier.where(type.coding.code = 'ACSN' and system = 'Onconova').exists()}o-pat-req-2:The identifier element must contain the identifier for the clinical center's patient identifier slice. {identifier.where(type.coding.code = 'MR').exists(system.exists() and value.exists())}o-pat-req-3:The gender element is required and must be provided {gender.exists()}o-pat-req-4:The birthDate element is required and must be provided {birthDate.exists() and birthDate.hasValue()}o-pat-req-5:The vital status extension is required and must be provided. {deceased.extension('http://onconova.github.io/fhir/StructureDefinition/onconova-ext-cancer-patient-vital-status').valueCodeableConcept.exists()}o-pat-req-6:If the patient is deceased, the date of death and cause of death must be provided. {deceasedDateTime.extension('http://onconova.github.io/fhir/StructureDefinition/onconova-ext-cancer-patient-vital-status').valueCodeableConcept.coding.code = '419099009' implies (deceasedDateTime.hasValue() and deceasedDateTime.extension('http://onconova.github.io/fhir/StructureDefinition/onconova-ext-cancer-patient-cause-of-death').valueCodeableConcept.exists())}o-pat-req-7:If the patient vital status is unknown, the end of records must be provided. {deceasedDateTime.extension('http://onconova.github.io/fhir/StructureDefinition/onconova-ext-cancer-patient-vital-status').valueCodeableConcept.coding.code = '261665006' implies extension('http://onconova.github.io/fhir/StructureDefinition/onconova-ext-cancer-patient-end-of-records').valueDate.hasValue()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T19:05:31+00:00</t>
+    <t>2026-04-16T05:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-cancer-patient.xlsx
+++ b/StructureDefinition-onconova-cancer-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T05:59:15+00:00</t>
+    <t>2026-04-26T18:09:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
